--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N74_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N74_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.18366954725687</v>
+        <v>7.829846301429241</v>
       </c>
       <c r="D2" t="n">
-        <v>48.39708046988351</v>
+        <v>7.86452557635607</v>
       </c>
       <c r="E2" t="n">
-        <v>7.407928068137609</v>
+        <v>1.203788311072362</v>
       </c>
       <c r="F2" t="n">
-        <v>10.85473019966785</v>
+        <v>1.763893657446025</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.55729451196233</v>
+        <v>6.428060358193878</v>
       </c>
       <c r="D3" t="n">
-        <v>27.34550389328515</v>
+        <v>4.443644382658837</v>
       </c>
       <c r="E3" t="n">
-        <v>7.407928068137609</v>
+        <v>1.203788311072362</v>
       </c>
       <c r="F3" t="n">
-        <v>10.85473019966785</v>
+        <v>1.763893657446025</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.04523221287971</v>
+        <v>4.882350234592953</v>
       </c>
       <c r="D4" t="n">
-        <v>23.80585235860592</v>
+        <v>3.868451008273462</v>
       </c>
       <c r="E4" t="n">
-        <v>7.407928068137609</v>
+        <v>1.203788311072362</v>
       </c>
       <c r="F4" t="n">
-        <v>10.85473019966785</v>
+        <v>1.763893657446025</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
